--- a/artfynd/A 34205-2025 artfynd.xlsx
+++ b/artfynd/A 34205-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136396600</v>
       </c>
       <c r="B2" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34205-2025 artfynd.xlsx
+++ b/artfynd/A 34205-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136396600</v>
       </c>
       <c r="B2" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34205-2025 artfynd.xlsx
+++ b/artfynd/A 34205-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136396600</v>
       </c>
       <c r="B2" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136396630</v>
       </c>
       <c r="B3" t="n">
-        <v>79560</v>
+        <v>79562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136396646</v>
       </c>
       <c r="B4" t="n">
-        <v>79560</v>
+        <v>79562</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34205-2025 artfynd.xlsx
+++ b/artfynd/A 34205-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136396600</v>
       </c>
       <c r="B2" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34205-2025 artfynd.xlsx
+++ b/artfynd/A 34205-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136396600</v>
       </c>
       <c r="B2" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136396630</v>
       </c>
       <c r="B3" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136396646</v>
       </c>
       <c r="B4" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34205-2025 artfynd.xlsx
+++ b/artfynd/A 34205-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136396600</v>
       </c>
       <c r="B2" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136396630</v>
       </c>
       <c r="B3" t="n">
-        <v>79566</v>
+        <v>79568</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136396646</v>
       </c>
       <c r="B4" t="n">
-        <v>79566</v>
+        <v>79568</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
